--- a/education_forms/046_english_medium_student_registration_form--education_forms.xlsx
+++ b/education_forms/046_english_medium_student_registration_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'a',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'A', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'b',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'B', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'c',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'C', 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'unknown',_'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Unknown', 'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'english',_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'English', 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'hindi',_'label':_'hindi'}</t>
+          <t>hindi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Hindi', 'label': 'Hindi'}</t>
+          <t>Hindi</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'bengali',_'label':_'bengali'}</t>
+          <t>bengali</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Bengali', 'label': 'Bengali'}</t>
+          <t>Bengali</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'marathi',_'label':_'marathi'}</t>
+          <t>marathi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Marathi', 'label': 'Marathi'}</t>
+          <t>Marathi</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'punjabi',_'label':_'punjabi'}</t>
+          <t>punjabi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Punjabi', 'label': 'Punjabi'}</t>
+          <t>Punjabi</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'tamil',_'label':_'tamil'}</t>
+          <t>tamil</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Tamil', 'label': 'Tamil'}</t>
+          <t>Tamil</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'telugu',_'label':_'telugu'}</t>
+          <t>telugu</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Telugu', 'label': 'Telugu'}</t>
+          <t>Telugu</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'kannada',_'label':_'kannada'}</t>
+          <t>kannada</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Kannada', 'label': 'Kannada'}</t>
+          <t>Kannada</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'kashmiri',_'label':_'kashmiri'}</t>
+          <t>kashmiri</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Kashmiri', 'label': 'Kashmiri'}</t>
+          <t>Kashmiri</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'kannada',_'label':_'kannada'}</t>
+          <t>sanskrit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Kannada', 'label': 'Kannada'}</t>
+          <t>Sanskrit</t>
         </is>
       </c>
     </row>
@@ -1035,29 +1035,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'sanskrit',_'label':_'sanskrit'}</t>
+          <t>tulu</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Sanskrit', 'label': 'Sanskrit'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>medium_of_instruction_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'value':_'tulu',_'label':_'tulu'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'value': 'Tulu', 'label': 'Tulu'}</t>
+          <t>Tulu</t>
         </is>
       </c>
     </row>
